--- a/Outputs/Scenarios/PtX_demand_EE_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EE_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0003495342219082036</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00126691832694766</v>
+        <v>0.001373432080341904</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002111530544912767</v>
+        <v>0.001994740306638541</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>5.036196475490044e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0008446122179651068</v>
+        <v>0.0008548887028450889</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0005174428610021083</v>
       </c>
       <c r="K30" t="n">
-        <v>0.006838011754025993</v>
+        <v>0.007412904611902663</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01139668625670999</v>
+        <v>0.01076632753106212</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>2.723383478958465e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.004558674502683996</v>
+        <v>0.004614140370455195</v>
       </c>
     </row>
     <row r="43">
